--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486469_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486469_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6721</v>
+        <v>7.6336</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0613</v>
+        <v>5.8378</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6108</v>
+        <v>1.7957</v>
       </c>
       <c r="G2" t="n">
         <v>3.7931</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.8742</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1476</v>
+        <v>0.9241</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2348</v>
+        <v>-0.0499</v>
       </c>
       <c r="V2" t="n">
         <v>1.0087</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1102</v>
+        <v>6.0389</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5818</v>
+        <v>7.1406</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4716</v>
+        <v>-1.1017</v>
       </c>
       <c r="G3" t="n">
         <v>5.6902</v>
@@ -688,13 +688,13 @@
         <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3939</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0601</v>
+        <v>0.6189</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.454</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>-1.056</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9611</v>
+        <v>4.4582</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7069</v>
+        <v>5.2657</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7458</v>
+        <v>-0.8075</v>
       </c>
       <c r="G4" t="n">
         <v>5.3787</v>
@@ -766,13 +766,13 @@
         <v>1.9576</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5927</v>
+        <v>-0.0955</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.822</v>
+        <v>-0.2632</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2293</v>
+        <v>0.1676</v>
       </c>
       <c r="V4" t="n">
         <v>-1.695</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5687</v>
+        <v>3.1872</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5408</v>
+        <v>1.6526</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0279</v>
+        <v>1.5347</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7857</v>
@@ -844,13 +844,13 @@
         <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4762</v>
+        <v>1.0947</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5396</v>
+        <v>0.6513</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9366</v>
+        <v>0.4434</v>
       </c>
       <c r="V5" t="n">
         <v>2.8782</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>A. ZUBIZARRETA ARANBARRI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5024</v>
+        <v>2.8119</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8633</v>
+        <v>1.3664</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6391</v>
+        <v>1.4455</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8966</v>
+        <v>1.8168</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0711</v>
+        <v>1.6758</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8255</v>
+        <v>0.141</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2593</v>
+        <v>1.5547</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6274</v>
+        <v>1.4782</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6319</v>
+        <v>0.0765</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6373</v>
+        <v>0.2621</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4437</v>
+        <v>0.1976</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1936</v>
+        <v>0.0645</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.6976</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.3501</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1734</v>
+        <v>-0.1349</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8242</v>
+        <v>-0.2307</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3492</v>
+        <v>0.0958</v>
       </c>
       <c r="V6" t="n">
         <v>1.13</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ZUBIZARRETA ARANBARRI</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.546</v>
+        <v>2.1267</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2547</v>
+        <v>-0.1425</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2914</v>
+        <v>2.2692</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8168</v>
+        <v>2.8966</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6758</v>
+        <v>2.0711</v>
       </c>
       <c r="I7" t="n">
-        <v>0.141</v>
+        <v>0.8255</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5547</v>
+        <v>2.2593</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4782</v>
+        <v>1.6274</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0765</v>
+        <v>0.6319</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2621</v>
+        <v>0.6373</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1976</v>
+        <v>0.4437</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0645</v>
+        <v>0.1936</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-3.6976</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>-4.3501</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4008</v>
+        <v>1.7977</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3425</v>
+        <v>0.8184</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0583</v>
+        <v>0.9794</v>
       </c>
       <c r="V7" t="n">
         <v>1.13</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4152</v>
+        <v>2.0914</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1945</v>
+        <v>1.7474</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2207</v>
+        <v>0.344</v>
       </c>
       <c r="G8" t="n">
         <v>3.1492</v>
@@ -1078,13 +1078,13 @@
         <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1697</v>
+        <v>0.846</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1476</v>
+        <v>0.7006</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0221</v>
+        <v>0.1454</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2512</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2309</v>
+        <v>-0.2046</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4817</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2509</v>
+        <v>-1.1276</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6862</v>
@@ -1156,13 +1156,13 @@
         <v>2.3926</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2108</v>
+        <v>-0.2247</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8736</v>
+        <v>0.3149</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6629</v>
+        <v>-0.5396</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6863</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1355</v>
+        <v>-2.7694</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2887</v>
+        <v>-2.9534</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1532</v>
+        <v>0.184</v>
       </c>
       <c r="G10" t="n">
         <v>-1.764</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4145</v>
+        <v>-0.0484</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6165</v>
+        <v>-0.2812</v>
       </c>
       <c r="U10" t="n">
-        <v>0.202</v>
+        <v>0.2328</v>
       </c>
       <c r="V10" t="n">
         <v>-0.7395</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5698</v>
+        <v>-4.0726</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5979</v>
+        <v>-3.0391</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9719</v>
+        <v>-1.0335</v>
       </c>
       <c r="G11" t="n">
         <v>-4.6112</v>
@@ -1312,13 +1312,13 @@
         <v>1.7401</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5686</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.1947</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1848</v>
+        <v>0.1232</v>
       </c>
       <c r="V11" t="n">
         <v>-1.13</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>21.3013</v>
+        <v>21.30129999999999</v>
       </c>
       <c r="E12" t="n">
         <v>17.7984</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5029</v>
+        <v>3.502800000000001</v>
       </c>
       <c r="G12" t="n">
         <v>13.8775</v>
@@ -1390,10 +1390,10 @@
         <v>15.2255</v>
       </c>
       <c r="S12" t="n">
-        <v>4.5724</v>
+        <v>4.572399999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>3.0582</v>
+        <v>3.0584</v>
       </c>
       <c r="U12" t="n">
         <v>1.514</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0095</v>
+        <v>0.5377</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0794</v>
+        <v>1.7499</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0889</v>
+        <v>-1.2122</v>
       </c>
       <c r="G13" t="n">
         <v>1.5871</v>
@@ -1468,13 +1468,13 @@
         <v>2.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8343</v>
+        <v>-1.287</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4384</v>
+        <v>-0.7679</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3959</v>
+        <v>-0.5191</v>
       </c>
       <c r="V13" t="n">
         <v>1.3252</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. KASIBABU SHILALA</t>
+          <t>D. MANCHON CRESPO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.8973</v>
+        <v>-0.2898</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3367</v>
+        <v>2.2143</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.2341</v>
+        <v>-2.5041</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.6222</v>
+        <v>-0.9686</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.332</v>
+        <v>-0.0609</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2901</v>
+        <v>-0.9076</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6085</v>
+        <v>2.282</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6268</v>
+        <v>1.1529</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0183</v>
+        <v>1.1292</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.2307</v>
+        <v>-3.2506</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.9589</v>
+        <v>-1.2138</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.2718</v>
+        <v>-2.0368</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6525</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2676</v>
+        <v>-0.9286</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8158</v>
+        <v>-0.1526</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5482</v>
+        <v>-0.776</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1952</v>
+        <v>2.2599</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.9754</v>
+        <v>-0.9560999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3924</v>
+        <v>-0.2806</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.583</v>
+        <v>-0.6755</v>
       </c>
       <c r="G15" t="n">
         <v>-1.3282</v>
@@ -1624,13 +1624,13 @@
         <v>0.435</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1438</v>
+        <v>0.1631</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1815</v>
+        <v>-0.0697</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3253</v>
+        <v>0.2328</v>
       </c>
       <c r="V15" t="n">
         <v>-0.226</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.3527</v>
+        <v>-1.4452</v>
       </c>
       <c r="E16" t="n">
         <v>-1.3856</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0329</v>
+        <v>-0.0596</v>
       </c>
       <c r="G16" t="n">
         <v>-0.6264999999999999</v>
@@ -1702,13 +1702,13 @@
         <v>0.2175</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1438</v>
+        <v>0.0514</v>
       </c>
       <c r="T16" t="n">
         <v>-0.137</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2808</v>
+        <v>0.1884</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. MANCHON CRESPO</t>
+          <t>J. KASIBABU SHILALA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4111</v>
+        <v>-2.4118</v>
       </c>
       <c r="E17" t="n">
-        <v>1.432</v>
+        <v>-0.1161</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.8431</v>
+        <v>-2.2957</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9686</v>
+        <v>-2.6222</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0609</v>
+        <v>-1.332</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9076</v>
+        <v>-1.2901</v>
       </c>
       <c r="J17" t="n">
-        <v>2.282</v>
+        <v>0.6085</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1529</v>
+        <v>0.6268</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1292</v>
+        <v>-0.0183</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.2506</v>
+        <v>-3.2307</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2138</v>
+        <v>-1.9589</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.0368</v>
+        <v>-1.2718</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6525</v>
+        <v>0.6525</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.05</v>
+        <v>-0.2469</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9349</v>
+        <v>0.3629</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1151</v>
+        <v>-0.6099</v>
       </c>
       <c r="V17" t="n">
-        <v>2.2599</v>
+        <v>-0.1952</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4525</v>
+        <v>-2.4217</v>
       </c>
       <c r="E18" t="n">
         <v>0.1897</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.6422</v>
+        <v>-2.6113</v>
       </c>
       <c r="G18" t="n">
         <v>-1.4836</v>
@@ -1858,13 +1858,13 @@
         <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7005</v>
+        <v>-0.6696</v>
       </c>
       <c r="T18" t="n">
         <v>-0.6609</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0395</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>-1.356</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4466</v>
+        <v>-3.4581</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3736</v>
+        <v>-2.2619</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.073</v>
+        <v>-1.1963</v>
       </c>
       <c r="G19" t="n">
         <v>-2.6756</v>
@@ -1936,13 +1936,13 @@
         <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1747</v>
+        <v>-0.1863</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1815</v>
+        <v>-0.0697</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0067</v>
+        <v>-0.1166</v>
       </c>
       <c r="V19" t="n">
         <v>0.7088</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.6791</v>
+        <v>-3.866</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.596</v>
+        <v>-0.8137</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0831</v>
+        <v>-3.0522</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4302</v>
@@ -2014,13 +2014,13 @@
         <v>2.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.086</v>
+        <v>-1.2729</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3014</v>
+        <v>-0.5191</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7846</v>
+        <v>-0.7538</v>
       </c>
       <c r="V20" t="n">
         <v>0.9247</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.077</v>
+        <v>-6.9904</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.793</v>
+        <v>-2.7988</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.284</v>
+        <v>-4.1915</v>
       </c>
       <c r="G21" t="n">
         <v>-3.3295</v>
@@ -2092,13 +2092,13 @@
         <v>1.7401</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7178</v>
+        <v>-0.1956</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5057</v>
+        <v>0.4999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.788</v>
+        <v>-0.6955</v>
       </c>
       <c r="V21" t="n">
         <v>-3.0302</v>
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-21.3012</v>
+        <v>-21.3014</v>
       </c>
       <c r="E22" t="n">
         <v>-3.5028</v>
       </c>
       <c r="F22" t="n">
-        <v>-17.7985</v>
+        <v>-17.7984</v>
       </c>
       <c r="G22" t="n">
         <v>-13.8773</v>
       </c>
       <c r="H22" t="n">
-        <v>-6.872800000000001</v>
+        <v>-6.8728</v>
       </c>
       <c r="I22" t="n">
         <v>-7.0044</v>
@@ -2170,13 +2170,13 @@
         <v>11.9629</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.5725</v>
+        <v>-4.572399999999999</v>
       </c>
       <c r="T22" t="n">
         <v>-1.5141</v>
       </c>
       <c r="U22" t="n">
-        <v>-3.0585</v>
+        <v>-3.0584</v>
       </c>
       <c r="V22" t="n">
         <v>0.4112</v>
